--- a/CDSE-WRD- Smt Rupali Thombre/data/dam-database.xlsx
+++ b/CDSE-WRD- Smt Rupali Thombre/data/dam-database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndsa0\Downloads\CDSE-Form--main (3)\CDSE-Form--main\CDSE-WRD- Smt Rupali Thombre\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndsa0\Downloads\CDSE-Form--main (6)\CDSE-Form--main\CDSE-WRD- Smt Rupali Thombre\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62736991-2094-4F00-AE9E-8F815AEFD57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BE1FA7-F9E0-411C-8C11-1D9B63812038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Dam Master Database" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dam Master Database'!$A$1:$CN$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dam Master Database'!$A$1:$CN$38</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3117" uniqueCount="974">
   <si>
     <t>PIC</t>
   </si>
@@ -2237,15 +2237,730 @@
   </si>
   <si>
     <t>• OGEE SPILLWAY/1(745)</t>
+  </si>
+  <si>
+    <t>MH09LH0687</t>
+  </si>
+  <si>
+    <t>GUTTEWADI</t>
+  </si>
+  <si>
+    <t>WRD-SE, Command Area Development Authority, Beed</t>
+  </si>
+  <si>
+    <t>18° 45' 5"</t>
+  </si>
+  <si>
+    <t>76° 39' 48"</t>
+  </si>
+  <si>
+    <t>Local river</t>
+  </si>
+  <si>
+    <t>14.35</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>1.813</t>
+  </si>
+  <si>
+    <t>1.698</t>
+  </si>
+  <si>
+    <t>576.25</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>A. S. Londhe</t>
+  </si>
+  <si>
+    <t>deisdambajogai@gmail.com</t>
+  </si>
+  <si>
+    <t>9422612713</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(208.5)</t>
+  </si>
+  <si>
+    <t>• ASPHALT (1)</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>160-SE Level-CADA, Beed (1)</t>
+  </si>
+  <si>
+    <t>Shri. S. M. Shri. Vivek</t>
+  </si>
+  <si>
+    <t>Tidke Prof. Mrs</t>
+  </si>
+  <si>
+    <t>MH09MH1005</t>
+  </si>
+  <si>
+    <t>BORNA</t>
+  </si>
+  <si>
+    <t>18° 51' 33"</t>
+  </si>
+  <si>
+    <t>76° 36' 1.50"</t>
+  </si>
+  <si>
+    <t>LOCAL NALLA</t>
+  </si>
+  <si>
+    <t>Parbhani</t>
+  </si>
+  <si>
+    <t>21.65</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>10.81</t>
+  </si>
+  <si>
+    <t>0.0219</t>
+  </si>
+  <si>
+    <t>8.972</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>441.45</t>
+  </si>
+  <si>
+    <t>439.45</t>
+  </si>
+  <si>
+    <t>JAYANT R. INAMDAR</t>
+  </si>
+  <si>
+    <t>eemid.parli@wrd.maharashtra.gov.in</t>
+  </si>
+  <si>
+    <t>9423441556</t>
+  </si>
+  <si>
+    <t>110.59</t>
+  </si>
+  <si>
+    <t>1246</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(471)</t>
+  </si>
+  <si>
+    <t>2088</t>
+  </si>
+  <si>
+    <t>MH09LH1055</t>
+  </si>
+  <si>
+    <t>KATKERWADI</t>
+  </si>
+  <si>
+    <t>18° 43' 42"</t>
+  </si>
+  <si>
+    <t>76° 42' 51"</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>754</t>
+  </si>
+  <si>
+    <t>1.582</t>
+  </si>
+  <si>
+    <t>1.294</t>
+  </si>
+  <si>
+    <t>470.7</t>
+  </si>
+  <si>
+    <t>543.7</t>
+  </si>
+  <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>25.02</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>MH09MH1603</t>
+  </si>
+  <si>
+    <t>DAITHANA</t>
+  </si>
+  <si>
+    <t>18° 47' 48"</t>
+  </si>
+  <si>
+    <t>76° 39' 32"</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>16.76</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>1.652</t>
+  </si>
+  <si>
+    <t>1.625</t>
+  </si>
+  <si>
+    <t>493.1</t>
+  </si>
+  <si>
+    <t>491.1</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>270.2622</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>MH09MH0133</t>
+  </si>
+  <si>
+    <t>WAN</t>
+  </si>
+  <si>
+    <t>18° 52' 11"</t>
+  </si>
+  <si>
+    <t>76° 26' 0"</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>2805</t>
+  </si>
+  <si>
+    <t>83.46</t>
+  </si>
+  <si>
+    <t>0.0346</t>
+  </si>
+  <si>
+    <t>81.955</t>
+  </si>
+  <si>
+    <t>Irrigation / Water Supply / Industrial</t>
+  </si>
+  <si>
+    <t>3874</t>
+  </si>
+  <si>
+    <t>455.98</t>
+  </si>
+  <si>
+    <t>454.88</t>
+  </si>
+  <si>
+    <t>379.92</t>
+  </si>
+  <si>
+    <t>2348</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(2348)</t>
+  </si>
+  <si>
+    <t>11426</t>
+  </si>
+  <si>
+    <t>Chief Engineer, Special Projects (SP), Water Resources Department - Amravati (M Corp.)</t>
+  </si>
+  <si>
+    <t>8118</t>
+  </si>
+  <si>
+    <t>MH09MH0265</t>
+  </si>
+  <si>
+    <t>BODHEGAON</t>
+  </si>
+  <si>
+    <t>18° 51' 34.45"</t>
+  </si>
+  <si>
+    <t>76° 21' 33.88"</t>
+  </si>
+  <si>
+    <t>760</t>
+  </si>
+  <si>
+    <t>4.199</t>
+  </si>
+  <si>
+    <t>3.65</t>
+  </si>
+  <si>
+    <t>750.56</t>
+  </si>
+  <si>
+    <t>505.2</t>
+  </si>
+  <si>
+    <t>503.25</t>
+  </si>
+  <si>
+    <t>J.R. Inamdar</t>
+  </si>
+  <si>
+    <t>eemidparli@gmail.com</t>
+  </si>
+  <si>
+    <t>45.58</t>
+  </si>
+  <si>
+    <t>750.8</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(750.56)</t>
+  </si>
+  <si>
+    <t>2761</t>
+  </si>
+  <si>
+    <t>MH292MH3439</t>
+  </si>
+  <si>
+    <t>Gopalpur</t>
+  </si>
+  <si>
+    <t>18° 53' 18"</t>
+  </si>
+  <si>
+    <t>76° 23' 12"</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>Beed</t>
+  </si>
+  <si>
+    <t>11.85</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>1.419</t>
+  </si>
+  <si>
+    <t>1.313</t>
+  </si>
+  <si>
+    <t>192.95</t>
+  </si>
+  <si>
+    <t>450.35</t>
+  </si>
+  <si>
+    <t>449.35</t>
+  </si>
+  <si>
+    <t>ANIL S. LONDHE</t>
+  </si>
+  <si>
+    <t>192.957</t>
+  </si>
+  <si>
+    <t>MH09MH1571</t>
+  </si>
+  <si>
+    <t>KALWATI</t>
+  </si>
+  <si>
+    <t>18° 16' 12"</t>
+  </si>
+  <si>
+    <t>76° 20' 6"</t>
+  </si>
+  <si>
+    <t>Local River</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>1.415</t>
+  </si>
+  <si>
+    <t>2.52869e-06</t>
+  </si>
+  <si>
+    <t>1.243</t>
+  </si>
+  <si>
+    <t>163.72</t>
+  </si>
+  <si>
+    <t>576.55</t>
+  </si>
+  <si>
+    <t>575.4</t>
+  </si>
+  <si>
+    <t>Shri. J. R. Inamdar</t>
+  </si>
+  <si>
+    <t>0.419</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>0.0003069</t>
+  </si>
+  <si>
+    <t>• OTHER/1(163.72)</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>MH09MH1577</t>
+  </si>
+  <si>
+    <t>SAKUD</t>
+  </si>
+  <si>
+    <t>18° 46' 36.07"</t>
+  </si>
+  <si>
+    <t>76° 26' 26.97"</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>1.915</t>
+  </si>
+  <si>
+    <t>1.695</t>
+  </si>
+  <si>
+    <t>224.91</t>
+  </si>
+  <si>
+    <t>573</t>
+  </si>
+  <si>
+    <t>571</t>
+  </si>
+  <si>
+    <t>J. R. Inamar</t>
+  </si>
+  <si>
+    <t>244622313</t>
+  </si>
+  <si>
+    <t>11.31</t>
+  </si>
+  <si>
+    <t>224.9197</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(224)</t>
+  </si>
+  <si>
+    <t>MH09MH1661</t>
+  </si>
+  <si>
+    <t>CHANAI</t>
+  </si>
+  <si>
+    <t>18° 44' 17"</t>
+  </si>
+  <si>
+    <t>76° 19' 49"</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>15.83</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>0.601</t>
+  </si>
+  <si>
+    <t>9.03e-05</t>
+  </si>
+  <si>
+    <t>0.542</t>
+  </si>
+  <si>
+    <t>64.088</t>
+  </si>
+  <si>
+    <t>638.88</t>
+  </si>
+  <si>
+    <t>637.88</t>
+  </si>
+  <si>
+    <t>J. R. Inamdar</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3.095</t>
+  </si>
+  <si>
+    <t>0.00903</t>
+  </si>
+  <si>
+    <t>64.88</t>
+  </si>
+  <si>
+    <t>• OTHER/1(64.002)</t>
+  </si>
+  <si>
+    <t>MH09MH2298</t>
+  </si>
+  <si>
+    <t>Sakud S.T.- 2</t>
+  </si>
+  <si>
+    <t>WRD-SE, Beed Irrigation Project Circle, Parli Vaijnath</t>
+  </si>
+  <si>
+    <t>18° 46' 27"</t>
+  </si>
+  <si>
+    <t>76° 25' 2"</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>16.68</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>0.6998</t>
+  </si>
+  <si>
+    <t>0.00178</t>
+  </si>
+  <si>
+    <t>0.6521</t>
+  </si>
+  <si>
+    <t>Irrigation / Water Supply</t>
+  </si>
+  <si>
+    <t>98.39</t>
+  </si>
+  <si>
+    <t>569.7</t>
+  </si>
+  <si>
+    <t>568.2</t>
+  </si>
+  <si>
+    <t>Tanaji Sopanrao Sawant</t>
+  </si>
+  <si>
+    <t>misd_ambjg@gmail.com</t>
+  </si>
+  <si>
+    <t>9423339661</t>
+  </si>
+  <si>
+    <t>0.0553</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>• OGEE SPILLWAY/1(98.39)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>MH09LH0288</t>
+  </si>
+  <si>
+    <t>GOSAIKANADI</t>
+  </si>
+  <si>
+    <t>18° 41' 33"</t>
+  </si>
+  <si>
+    <t>76° 18' 42"</t>
+  </si>
+  <si>
+    <t>Jalna</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>2.266</t>
+  </si>
+  <si>
+    <t>2.102</t>
+  </si>
+  <si>
+    <t>278.94</t>
+  </si>
+  <si>
+    <t>658.97</t>
+  </si>
+  <si>
+    <t>656.87</t>
+  </si>
+  <si>
+    <t>A. S. londhe</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>MH09LH0709</t>
+  </si>
+  <si>
+    <t>DIGHOL</t>
+  </si>
+  <si>
+    <t>76° 16' 50"</t>
+  </si>
+  <si>
+    <t>11.44</t>
+  </si>
+  <si>
+    <t>1460</t>
+  </si>
+  <si>
+    <t>2.231</t>
+  </si>
+  <si>
+    <t>1.99</t>
+  </si>
+  <si>
+    <t>131.4</t>
+  </si>
+  <si>
+    <t>642.22</t>
+  </si>
+  <si>
+    <t>641</t>
+  </si>
+  <si>
+    <t>A. S Londhe</t>
+  </si>
+  <si>
+    <t>20.07</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>MH09MH1596</t>
+  </si>
+  <si>
+    <t>NIL KANTESHWAR</t>
+  </si>
+  <si>
+    <t>18° 44' 18"</t>
+  </si>
+  <si>
+    <t>76° 20' 46"</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>1.96</t>
+  </si>
+  <si>
+    <t>1.533</t>
+  </si>
+  <si>
+    <t>475.843</t>
+  </si>
+  <si>
+    <t>642.3</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>26.25</t>
+  </si>
+  <si>
+    <t>609</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2417,8 +3132,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="36">
+  <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
@@ -2455,31 +3172,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="24" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="24" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="24" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="24" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="34" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="36" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="36">
+  <cellStyles count="38">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="16" xr:uid="{492FBBFB-725C-478D-9713-DDE3ED5B18A5}"/>
     <cellStyle name="Normal 11" xfId="18" xr:uid="{7D9BEA0D-DABB-4777-8031-969A28387181}"/>
@@ -2501,6 +3215,7 @@
     <cellStyle name="Normal 2 16" xfId="31" xr:uid="{35AB1345-C533-405C-A59F-2AA9514A7929}"/>
     <cellStyle name="Normal 2 17" xfId="33" xr:uid="{F20834A4-BC6B-40C9-9E3F-C7FB33EB713E}"/>
     <cellStyle name="Normal 2 18" xfId="35" xr:uid="{ECC123EA-B4E8-429B-B358-0391864499E2}"/>
+    <cellStyle name="Normal 2 19" xfId="37" xr:uid="{9DCF4A7C-97C2-406B-9E01-B926B20C0547}"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{8B1DEF3D-BCED-4E38-890C-D9BD6F497AA3}"/>
     <cellStyle name="Normal 2 3" xfId="5" xr:uid="{5F93C9D9-8B3B-4A3D-A6C5-31E9C2C78311}"/>
     <cellStyle name="Normal 2 4" xfId="7" xr:uid="{C554FB65-C464-4E6C-80BD-882ED78889F0}"/>
@@ -2509,6 +3224,7 @@
     <cellStyle name="Normal 2 7" xfId="13" xr:uid="{B9C0472B-5A47-458B-859F-1ACB3ED30369}"/>
     <cellStyle name="Normal 2 8" xfId="15" xr:uid="{26B2267D-2DEA-4538-AEEC-830BD65F8FCA}"/>
     <cellStyle name="Normal 2 9" xfId="17" xr:uid="{6A1A66F7-6531-49B5-BA19-5EA9D17321C3}"/>
+    <cellStyle name="Normal 20" xfId="36" xr:uid="{CB378ED3-4B1B-4EAD-A61C-746FF7F77EC6}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{C6E518C1-6E8C-45B9-B960-0A2D8197AC39}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{DEE877F6-4D1F-402A-A549-2831AA6FFA45}"/>
     <cellStyle name="Normal 5" xfId="6" xr:uid="{BEACDAAF-2574-463F-A5EA-E136314760AB}"/>
@@ -2852,7 +3568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C487F-CAE2-4631-9BDF-00AEA4D9F9CD}">
-  <dimension ref="A1:CD76"/>
+  <dimension ref="A1:CD75"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
@@ -3407,25 +4123,25 @@
       <c r="BW2" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX2" s="7" t="s">
+      <c r="BX2" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY2" s="7" t="s">
+      <c r="BY2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ2" s="7" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA2" s="7" t="s">
+      <c r="CA2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB2" s="7" t="s">
+      <c r="CB2" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC2" s="7" t="s">
+      <c r="CC2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD2" s="7">
+      <c r="CD2" s="6">
         <v>5114</v>
       </c>
     </row>
@@ -3655,25 +4371,25 @@
       <c r="BW3" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX3" s="7" t="s">
+      <c r="BX3" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY3" s="7" t="s">
+      <c r="BY3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ3" s="7" t="s">
+      <c r="BZ3" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA3" s="7" t="s">
+      <c r="CA3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB3" s="7" t="s">
+      <c r="CB3" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC3" s="7" t="s">
+      <c r="CC3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD3" s="7">
+      <c r="CD3" s="6">
         <v>4322</v>
       </c>
     </row>
@@ -3903,25 +4619,25 @@
       <c r="BW4" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX4" s="7" t="s">
+      <c r="BX4" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY4" s="7" t="s">
+      <c r="BY4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ4" s="7" t="s">
+      <c r="BZ4" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA4" s="7" t="s">
+      <c r="CA4" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB4" s="7" t="s">
+      <c r="CB4" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC4" s="7" t="s">
+      <c r="CC4" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD4" s="7">
+      <c r="CD4" s="6">
         <v>2458</v>
       </c>
     </row>
@@ -4151,25 +4867,25 @@
       <c r="BW5" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX5" s="7" t="s">
+      <c r="BX5" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY5" s="7" t="s">
+      <c r="BY5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ5" s="7" t="s">
+      <c r="BZ5" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA5" s="7" t="s">
+      <c r="CA5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB5" s="7" t="s">
+      <c r="CB5" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC5" s="7" t="s">
+      <c r="CC5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD5" s="7">
+      <c r="CD5" s="6">
         <v>4744</v>
       </c>
     </row>
@@ -4399,25 +5115,25 @@
       <c r="BW6" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX6" s="7" t="s">
+      <c r="BX6" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY6" s="7" t="s">
+      <c r="BY6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ6" s="7" t="s">
+      <c r="BZ6" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA6" s="7" t="s">
+      <c r="CA6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB6" s="7" t="s">
+      <c r="CB6" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC6" s="7" t="s">
+      <c r="CC6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD6" s="7">
+      <c r="CD6" s="6">
         <v>3029</v>
       </c>
     </row>
@@ -4647,25 +5363,25 @@
       <c r="BW7" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX7" s="7" t="s">
+      <c r="BX7" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY7" s="7" t="s">
+      <c r="BY7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ7" s="7" t="s">
+      <c r="BZ7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA7" s="7" t="s">
+      <c r="CA7" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB7" s="7" t="s">
+      <c r="CB7" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC7" s="7" t="s">
+      <c r="CC7" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD7" s="7">
+      <c r="CD7" s="6">
         <v>2050</v>
       </c>
     </row>
@@ -4895,25 +5611,25 @@
       <c r="BW8" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX8" s="7" t="s">
+      <c r="BX8" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY8" s="7" t="s">
+      <c r="BY8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ8" s="7" t="s">
+      <c r="BZ8" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA8" s="7" t="s">
+      <c r="CA8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB8" s="7" t="s">
+      <c r="CB8" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC8" s="7" t="s">
+      <c r="CC8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD8" s="7">
+      <c r="CD8" s="6">
         <v>5055</v>
       </c>
     </row>
@@ -5143,25 +5859,25 @@
       <c r="BW9" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX9" s="7" t="s">
+      <c r="BX9" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY9" s="7" t="s">
+      <c r="BY9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ9" s="7" t="s">
+      <c r="BZ9" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA9" s="7" t="s">
+      <c r="CA9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB9" s="7" t="s">
+      <c r="CB9" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC9" s="7" t="s">
+      <c r="CC9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD9" s="7">
+      <c r="CD9" s="6">
         <v>3392</v>
       </c>
     </row>
@@ -5391,25 +6107,25 @@
       <c r="BW10" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX10" s="7" t="s">
+      <c r="BX10" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY10" s="7" t="s">
+      <c r="BY10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ10" s="7" t="s">
+      <c r="BZ10" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA10" s="7" t="s">
+      <c r="CA10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB10" s="7" t="s">
+      <c r="CB10" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC10" s="7" t="s">
+      <c r="CC10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD10" s="7">
+      <c r="CD10" s="6">
         <v>2641</v>
       </c>
     </row>
@@ -5639,25 +6355,25 @@
       <c r="BW11" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX11" s="7" t="s">
+      <c r="BX11" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY11" s="7" t="s">
+      <c r="BY11" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ11" s="7" t="s">
+      <c r="BZ11" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA11" s="7" t="s">
+      <c r="CA11" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB11" s="7" t="s">
+      <c r="CB11" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC11" s="7" t="s">
+      <c r="CC11" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD11" s="7">
+      <c r="CD11" s="6">
         <v>5158</v>
       </c>
     </row>
@@ -5887,25 +6603,25 @@
       <c r="BW12" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX12" s="7" t="s">
+      <c r="BX12" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY12" s="7" t="s">
+      <c r="BY12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ12" s="7" t="s">
+      <c r="BZ12" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA12" s="7" t="s">
+      <c r="CA12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB12" s="7" t="s">
+      <c r="CB12" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC12" s="7" t="s">
+      <c r="CC12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD12" s="7">
+      <c r="CD12" s="6">
         <v>4035</v>
       </c>
     </row>
@@ -6135,25 +6851,25 @@
       <c r="BW13" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX13" s="7" t="s">
+      <c r="BX13" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY13" s="7" t="s">
+      <c r="BY13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ13" s="7" t="s">
+      <c r="BZ13" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA13" s="7" t="s">
+      <c r="CA13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB13" s="7" t="s">
+      <c r="CB13" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC13" s="7" t="s">
+      <c r="CC13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD13" s="7">
+      <c r="CD13" s="6">
         <v>1472</v>
       </c>
     </row>
@@ -6383,25 +7099,25 @@
       <c r="BW14" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX14" s="7" t="s">
+      <c r="BX14" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY14" s="7" t="s">
+      <c r="BY14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ14" s="7" t="s">
+      <c r="BZ14" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA14" s="7" t="s">
+      <c r="CA14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB14" s="7" t="s">
+      <c r="CB14" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC14" s="7" t="s">
+      <c r="CC14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD14" s="7">
+      <c r="CD14" s="6">
         <v>2056</v>
       </c>
     </row>
@@ -6631,25 +7347,25 @@
       <c r="BW15" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX15" s="7" t="s">
+      <c r="BX15" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY15" s="7" t="s">
+      <c r="BY15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ15" s="7" t="s">
+      <c r="BZ15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA15" s="7" t="s">
+      <c r="CA15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB15" s="7" t="s">
+      <c r="CB15" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC15" s="7" t="s">
+      <c r="CC15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD15" s="7">
+      <c r="CD15" s="6">
         <v>3320</v>
       </c>
     </row>
@@ -6879,25 +7595,25 @@
       <c r="BW16" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX16" s="7" t="s">
+      <c r="BX16" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY16" s="7" t="s">
+      <c r="BY16" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ16" s="7" t="s">
+      <c r="BZ16" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA16" s="7" t="s">
+      <c r="CA16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB16" s="7" t="s">
+      <c r="CB16" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC16" s="7" t="s">
+      <c r="CC16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD16" s="7">
+      <c r="CD16" s="6">
         <v>2328</v>
       </c>
     </row>
@@ -7127,25 +7843,25 @@
       <c r="BW17" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX17" s="7" t="s">
+      <c r="BX17" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY17" s="7" t="s">
+      <c r="BY17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ17" s="7" t="s">
+      <c r="BZ17" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA17" s="7" t="s">
+      <c r="CA17" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB17" s="7" t="s">
+      <c r="CB17" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC17" s="7" t="s">
+      <c r="CC17" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD17" s="7">
+      <c r="CD17" s="6">
         <v>4717</v>
       </c>
     </row>
@@ -7375,25 +8091,25 @@
       <c r="BW18" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX18" s="7" t="s">
+      <c r="BX18" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY18" s="7" t="s">
+      <c r="BY18" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ18" s="7" t="s">
+      <c r="BZ18" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA18" s="7" t="s">
+      <c r="CA18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB18" s="7" t="s">
+      <c r="CB18" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC18" s="7" t="s">
+      <c r="CC18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD18" s="7">
+      <c r="CD18" s="6">
         <v>2407</v>
       </c>
     </row>
@@ -7623,25 +8339,25 @@
       <c r="BW19" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX19" s="7" t="s">
+      <c r="BX19" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY19" s="7" t="s">
+      <c r="BY19" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ19" s="7" t="s">
+      <c r="BZ19" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA19" s="7" t="s">
+      <c r="CA19" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB19" s="7" t="s">
+      <c r="CB19" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC19" s="7" t="s">
+      <c r="CC19" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD19" s="7">
+      <c r="CD19" s="6">
         <v>3321</v>
       </c>
     </row>
@@ -7871,25 +8587,25 @@
       <c r="BW20" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX20" s="7" t="s">
+      <c r="BX20" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY20" s="7" t="s">
+      <c r="BY20" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ20" s="7" t="s">
+      <c r="BZ20" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA20" s="7" t="s">
+      <c r="CA20" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB20" s="7" t="s">
+      <c r="CB20" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC20" s="7" t="s">
+      <c r="CC20" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD20" s="7">
+      <c r="CD20" s="6">
         <v>3625</v>
       </c>
     </row>
@@ -8119,25 +8835,25 @@
       <c r="BW21" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX21" s="7" t="s">
+      <c r="BX21" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY21" s="7" t="s">
+      <c r="BY21" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ21" s="7" t="s">
+      <c r="BZ21" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA21" s="7" t="s">
+      <c r="CA21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB21" s="7" t="s">
+      <c r="CB21" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC21" s="7" t="s">
+      <c r="CC21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD21" s="7">
+      <c r="CD21" s="6">
         <v>2603</v>
       </c>
     </row>
@@ -8367,25 +9083,25 @@
       <c r="BW22" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX22" s="7" t="s">
+      <c r="BX22" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY22" s="7" t="s">
+      <c r="BY22" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ22" s="7" t="s">
+      <c r="BZ22" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA22" s="7" t="s">
+      <c r="CA22" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB22" s="7" t="s">
+      <c r="CB22" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC22" s="7" t="s">
+      <c r="CC22" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD22" s="7">
+      <c r="CD22" s="6">
         <v>3457</v>
       </c>
     </row>
@@ -8615,25 +9331,25 @@
       <c r="BW23" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX23" s="7" t="s">
+      <c r="BX23" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY23" s="7" t="s">
+      <c r="BY23" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ23" s="7" t="s">
+      <c r="BZ23" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA23" s="7" t="s">
+      <c r="CA23" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB23" s="7" t="s">
+      <c r="CB23" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC23" s="7" t="s">
+      <c r="CC23" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD23" s="7">
+      <c r="CD23" s="6">
         <v>1442</v>
       </c>
     </row>
@@ -8863,25 +9579,25 @@
       <c r="BW24" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX24" s="7" t="s">
+      <c r="BX24" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY24" s="7" t="s">
+      <c r="BY24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ24" s="7" t="s">
+      <c r="BZ24" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA24" s="7" t="s">
+      <c r="CA24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB24" s="7" t="s">
+      <c r="CB24" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC24" s="7" t="s">
+      <c r="CC24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD24" s="7">
+      <c r="CD24" s="6">
         <v>2756</v>
       </c>
     </row>
@@ -9111,25 +9827,25 @@
       <c r="BW25" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX25" s="7" t="s">
+      <c r="BX25" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY25" s="7" t="s">
+      <c r="BY25" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ25" s="7" t="s">
+      <c r="BZ25" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA25" s="7" t="s">
+      <c r="CA25" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB25" s="7" t="s">
+      <c r="CB25" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC25" s="7" t="s">
+      <c r="CC25" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD25" s="7">
+      <c r="CD25" s="6">
         <v>5738</v>
       </c>
     </row>
@@ -9359,25 +10075,25 @@
       <c r="BW26" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX26" s="7" t="s">
+      <c r="BX26" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY26" s="7" t="s">
+      <c r="BY26" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ26" s="7" t="s">
+      <c r="BZ26" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA26" s="7" t="s">
+      <c r="CA26" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB26" s="7" t="s">
+      <c r="CB26" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC26" s="7" t="s">
+      <c r="CC26" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD26" s="7">
+      <c r="CD26" s="6">
         <v>6543</v>
       </c>
     </row>
@@ -9607,25 +10323,25 @@
       <c r="BW27" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX27" s="7" t="s">
+      <c r="BX27" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY27" s="7" t="s">
+      <c r="BY27" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ27" s="7" t="s">
+      <c r="BZ27" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA27" s="7" t="s">
+      <c r="CA27" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB27" s="7" t="s">
+      <c r="CB27" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC27" s="7" t="s">
+      <c r="CC27" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD27" s="7" t="s">
+      <c r="CD27" s="6" t="s">
         <v>571</v>
       </c>
     </row>
@@ -9855,25 +10571,25 @@
       <c r="BW28" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX28" s="7" t="s">
+      <c r="BX28" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY28" s="7" t="s">
+      <c r="BY28" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ28" s="7" t="s">
+      <c r="BZ28" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA28" s="7" t="s">
+      <c r="CA28" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB28" s="7" t="s">
+      <c r="CB28" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC28" s="7" t="s">
+      <c r="CC28" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD28" s="7">
+      <c r="CD28" s="6">
         <v>6138</v>
       </c>
     </row>
@@ -10103,25 +10819,25 @@
       <c r="BW29" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BX29" s="7" t="s">
+      <c r="BX29" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY29" s="7" t="s">
+      <c r="BY29" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ29" s="7" t="s">
+      <c r="BZ29" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA29" s="7" t="s">
+      <c r="CA29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB29" s="7" t="s">
+      <c r="CB29" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC29" s="7" t="s">
+      <c r="CC29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD29" s="7">
+      <c r="CD29" s="6">
         <v>6659</v>
       </c>
     </row>
@@ -10351,25 +11067,25 @@
       <c r="BW30" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX30" s="7" t="s">
+      <c r="BX30" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY30" s="7" t="s">
+      <c r="BY30" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ30" s="7" t="s">
+      <c r="BZ30" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA30" s="7" t="s">
+      <c r="CA30" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB30" s="7" t="s">
+      <c r="CB30" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC30" s="7" t="s">
+      <c r="CC30" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD30" s="7">
+      <c r="CD30" s="6">
         <v>3748</v>
       </c>
     </row>
@@ -10599,25 +11315,25 @@
       <c r="BW31" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX31" s="7" t="s">
+      <c r="BX31" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY31" s="7" t="s">
+      <c r="BY31" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ31" s="7" t="s">
+      <c r="BZ31" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA31" s="7" t="s">
+      <c r="CA31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB31" s="7" t="s">
+      <c r="CB31" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC31" s="7" t="s">
+      <c r="CC31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD31" s="7">
+      <c r="CD31" s="6">
         <v>2962</v>
       </c>
     </row>
@@ -10847,25 +11563,25 @@
       <c r="BW32" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX32" s="7" t="s">
+      <c r="BX32" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY32" s="7" t="s">
+      <c r="BY32" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ32" s="7" t="s">
+      <c r="BZ32" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA32" s="7" t="s">
+      <c r="CA32" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB32" s="7" t="s">
+      <c r="CB32" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC32" s="7" t="s">
+      <c r="CC32" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD32" s="7">
+      <c r="CD32" s="6">
         <v>2231</v>
       </c>
     </row>
@@ -11095,25 +11811,25 @@
       <c r="BW33" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX33" s="7" t="s">
+      <c r="BX33" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY33" s="7" t="s">
+      <c r="BY33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ33" s="7" t="s">
+      <c r="BZ33" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA33" s="7" t="s">
+      <c r="CA33" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB33" s="7" t="s">
+      <c r="CB33" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC33" s="7" t="s">
+      <c r="CC33" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD33" s="7">
+      <c r="CD33" s="6">
         <v>1815</v>
       </c>
     </row>
@@ -11343,25 +12059,25 @@
       <c r="BW34" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX34" s="7" t="s">
+      <c r="BX34" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY34" s="7" t="s">
+      <c r="BY34" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ34" s="7" t="s">
+      <c r="BZ34" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA34" s="7" t="s">
+      <c r="CA34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB34" s="7" t="s">
+      <c r="CB34" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC34" s="7" t="s">
+      <c r="CC34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD34" s="7">
+      <c r="CD34" s="6">
         <v>2213</v>
       </c>
     </row>
@@ -11591,25 +12307,25 @@
       <c r="BW35" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX35" s="7" t="s">
+      <c r="BX35" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY35" s="7" t="s">
+      <c r="BY35" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ35" s="7" t="s">
+      <c r="BZ35" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA35" s="7" t="s">
+      <c r="CA35" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB35" s="7" t="s">
+      <c r="CB35" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC35" s="7" t="s">
+      <c r="CC35" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD35" s="7">
+      <c r="CD35" s="6">
         <v>2656</v>
       </c>
     </row>
@@ -11839,25 +12555,25 @@
       <c r="BW36" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX36" s="7" t="s">
+      <c r="BX36" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY36" s="7" t="s">
+      <c r="BY36" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ36" s="7" t="s">
+      <c r="BZ36" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA36" s="7" t="s">
+      <c r="CA36" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB36" s="7" t="s">
+      <c r="CB36" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC36" s="7" t="s">
+      <c r="CC36" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD36" s="7">
+      <c r="CD36" s="6">
         <v>2073</v>
       </c>
     </row>
@@ -12087,37 +12803,37 @@
       <c r="BW37" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="BX37" s="7" t="s">
+      <c r="BX37" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY37" s="7" t="s">
+      <c r="BY37" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ37" s="7" t="s">
+      <c r="BZ37" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="CA37" s="7" t="s">
+      <c r="CA37" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB37" s="7" t="s">
+      <c r="CB37" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="CC37" s="7" t="s">
+      <c r="CC37" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD37" s="7">
+      <c r="CD37" s="6">
         <v>2888</v>
       </c>
     </row>
     <row r="38" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>2307</v>
+        <v>1817</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>82</v>
@@ -12126,19 +12842,19 @@
         <v>82</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>83</v>
+        <v>740</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>99</v>
@@ -12150,10 +12866,10 @@
         <v>100</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>186</v>
+        <v>743</v>
+      </c>
+      <c r="O38" s="6">
+        <v>0</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>377</v>
@@ -12162,31 +12878,31 @@
         <v>102</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>178</v>
+        <v>745</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="U38" s="6" t="s">
         <v>90</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>729</v>
+        <v>747</v>
       </c>
       <c r="W38" s="6" t="s">
-        <v>445</v>
+        <v>91</v>
       </c>
       <c r="X38" s="6" t="s">
-        <v>730</v>
+        <v>687</v>
       </c>
       <c r="Y38" s="6" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="Z38" s="6" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="AA38" s="6" t="s">
         <v>92</v>
@@ -12195,13 +12911,13 @@
         <v>93</v>
       </c>
       <c r="AC38" s="6" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="AD38" s="6" t="s">
-        <v>340</v>
+        <v>751</v>
       </c>
       <c r="AE38" s="6" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="AF38" s="6">
         <v>0</v>
@@ -12210,13 +12926,13 @@
         <v>90</v>
       </c>
       <c r="AH38" s="6" t="s">
-        <v>735</v>
+        <v>174</v>
       </c>
       <c r="AI38" s="6" t="s">
         <v>90</v>
       </c>
       <c r="AJ38" s="6">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" s="6" t="s">
         <v>126</v>
@@ -12225,22 +12941,22 @@
         <v>0</v>
       </c>
       <c r="AM38" s="6" t="s">
-        <v>736</v>
+        <v>687</v>
       </c>
       <c r="AN38" s="6" t="s">
-        <v>540</v>
+        <v>155</v>
       </c>
       <c r="AO38" s="6" t="s">
         <v>92</v>
       </c>
       <c r="AP38" s="6">
-        <v>1.6</v>
+        <v>0.115</v>
       </c>
       <c r="AQ38" s="6" t="s">
         <v>115</v>
       </c>
       <c r="AR38" s="6" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="AS38" s="6">
         <v>0</v>
@@ -12261,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="AY38" s="6" t="s">
-        <v>105</v>
+        <v>754</v>
       </c>
       <c r="AZ38" s="6">
         <v>0</v>
@@ -12315,1223 +13031,3519 @@
         <v>92</v>
       </c>
       <c r="BQ38" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BR38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="BS38" s="6">
-        <v>0</v>
+        <v>93</v>
+      </c>
+      <c r="BS38" s="6" t="s">
+        <v>755</v>
       </c>
       <c r="BT38" s="6" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="BU38" s="6">
         <v>0</v>
       </c>
       <c r="BV38" s="6">
-        <v>9822220725</v>
+        <v>9423144198</v>
       </c>
       <c r="BW38" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="BX38" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX38" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BY38" s="7" t="s">
+      <c r="BY38" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BZ38" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="CA38" s="7" t="s">
+      <c r="BZ38" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA38" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CB38" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="CC38" s="7" t="s">
+      <c r="CB38" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC38" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="CD38" s="7">
-        <v>2090</v>
+      <c r="CD38" s="6">
+        <v>3857</v>
       </c>
     </row>
     <row r="39" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
-      <c r="V39" s="5"/>
-      <c r="W39" s="5"/>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5"/>
-      <c r="Z39" s="5"/>
-      <c r="AA39" s="5"/>
-      <c r="AB39" s="5"/>
-      <c r="AC39" s="5"/>
-      <c r="AD39" s="5"/>
-      <c r="AE39" s="5"/>
-      <c r="AF39" s="5"/>
-      <c r="AG39" s="5"/>
-      <c r="AH39" s="5"/>
-      <c r="AI39" s="5"/>
-      <c r="AJ39" s="5"/>
-      <c r="AK39" s="5"/>
-      <c r="AL39" s="5"/>
-      <c r="AM39" s="5"/>
-      <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
-      <c r="AP39" s="5"/>
-      <c r="AQ39" s="5"/>
-      <c r="AR39" s="5"/>
-      <c r="AS39" s="5"/>
-      <c r="AT39" s="5"/>
-      <c r="AU39" s="5"/>
-      <c r="AV39" s="5"/>
-      <c r="AW39" s="5"/>
-      <c r="AX39" s="5"/>
-      <c r="AY39" s="5"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="5"/>
-      <c r="BB39" s="5"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="5"/>
-      <c r="BE39" s="5"/>
-      <c r="BF39" s="5"/>
-      <c r="BG39" s="5"/>
-      <c r="BH39" s="5"/>
-      <c r="BI39" s="5"/>
-      <c r="BJ39" s="5"/>
-      <c r="BK39" s="5"/>
-      <c r="BL39" s="5"/>
-      <c r="BM39" s="5"/>
-      <c r="BN39" s="5"/>
-      <c r="BO39" s="5"/>
-      <c r="BP39" s="5"/>
-      <c r="BQ39" s="5"/>
-      <c r="BR39" s="5"/>
-      <c r="BS39" s="5"/>
-      <c r="BT39" s="5"/>
-      <c r="BU39" s="5"/>
-      <c r="BV39" s="5"/>
-      <c r="BW39" s="5"/>
-      <c r="BX39" s="1"/>
-      <c r="BY39" s="1"/>
-      <c r="BZ39" s="1"/>
-      <c r="CA39" s="1"/>
-      <c r="CB39" s="1"/>
-      <c r="CC39" s="1"/>
-      <c r="CD39" s="1"/>
+      <c r="A39" s="6">
+        <v>1818</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="O39" s="6">
+        <v>0</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="S39" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="T39" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="U39" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="W39" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X39" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="Y39" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="Z39" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="AA39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC39" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="AE39" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="AI39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK39" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="AN39" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="AO39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP39" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="AQ39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR39" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="AS39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY39" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="AZ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS39" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="BT39" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU39" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV39" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW39" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX39" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY39" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ39" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB39" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD39" s="6">
+        <v>4087</v>
+      </c>
     </row>
     <row r="40" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="5"/>
-      <c r="W40" s="5"/>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5"/>
-      <c r="Z40" s="5"/>
-      <c r="AA40" s="5"/>
-      <c r="AB40" s="5"/>
-      <c r="AC40" s="5"/>
-      <c r="AD40" s="5"/>
-      <c r="AE40" s="5"/>
-      <c r="AF40" s="5"/>
-      <c r="AG40" s="5"/>
-      <c r="AH40" s="5"/>
-      <c r="AI40" s="5"/>
-      <c r="AJ40" s="5"/>
-      <c r="AK40" s="5"/>
-      <c r="AL40" s="5"/>
-      <c r="AM40" s="5"/>
-      <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
-      <c r="AP40" s="5"/>
-      <c r="AQ40" s="5"/>
-      <c r="AR40" s="5"/>
-      <c r="AS40" s="5"/>
-      <c r="AT40" s="5"/>
-      <c r="AU40" s="5"/>
-      <c r="AV40" s="5"/>
-      <c r="AW40" s="5"/>
-      <c r="AX40" s="5"/>
-      <c r="AY40" s="5"/>
-      <c r="AZ40" s="5"/>
-      <c r="BA40" s="5"/>
-      <c r="BB40" s="5"/>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="5"/>
-      <c r="BE40" s="5"/>
-      <c r="BF40" s="5"/>
-      <c r="BG40" s="5"/>
-      <c r="BH40" s="5"/>
-      <c r="BI40" s="5"/>
-      <c r="BJ40" s="5"/>
-      <c r="BK40" s="5"/>
-      <c r="BL40" s="5"/>
-      <c r="BM40" s="5"/>
-      <c r="BN40" s="5"/>
-      <c r="BO40" s="5"/>
-      <c r="BP40" s="5"/>
-      <c r="BQ40" s="5"/>
-      <c r="BR40" s="5"/>
-      <c r="BS40" s="5"/>
-      <c r="BT40" s="5"/>
-      <c r="BU40" s="5"/>
-      <c r="BV40" s="5"/>
-      <c r="BW40" s="5"/>
-      <c r="BX40" s="1"/>
-      <c r="BY40" s="1"/>
-      <c r="BZ40" s="1"/>
-      <c r="CA40" s="1"/>
-      <c r="CB40" s="1"/>
-      <c r="CC40" s="1"/>
-      <c r="CD40" s="1"/>
+      <c r="A40" s="6">
+        <v>1819</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="O40" s="6">
+        <v>0</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="S40" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="T40" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="U40" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V40" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="W40" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X40" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="Y40" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="Z40" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC40" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="AD40" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="AE40" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="AF40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH40" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="AI40" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ40" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="AK40" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="AN40" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="AO40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP40" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AQ40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY40" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="AZ40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS40" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="BT40" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU40" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV40" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW40" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX40" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY40" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ40" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB40" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD40" s="6">
+        <v>3413</v>
+      </c>
     </row>
     <row r="41" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="5"/>
-      <c r="W41" s="5"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5"/>
-      <c r="Z41" s="5"/>
-      <c r="AA41" s="5"/>
-      <c r="AB41" s="5"/>
-      <c r="AC41" s="5"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="5"/>
-      <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
-      <c r="AH41" s="5"/>
-      <c r="AI41" s="5"/>
-      <c r="AJ41" s="5"/>
-      <c r="AK41" s="5"/>
-      <c r="AL41" s="5"/>
-      <c r="AM41" s="5"/>
-      <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
-      <c r="AP41" s="5"/>
-      <c r="AQ41" s="5"/>
-      <c r="AR41" s="5"/>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
-      <c r="AU41" s="5"/>
-      <c r="AV41" s="5"/>
-      <c r="AW41" s="5"/>
-      <c r="AX41" s="5"/>
-      <c r="AY41" s="5"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="5"/>
-      <c r="BB41" s="5"/>
-      <c r="BC41" s="5"/>
-      <c r="BD41" s="5"/>
-      <c r="BE41" s="5"/>
-      <c r="BF41" s="5"/>
-      <c r="BG41" s="5"/>
-      <c r="BH41" s="5"/>
-      <c r="BI41" s="5"/>
-      <c r="BJ41" s="5"/>
-      <c r="BK41" s="5"/>
-      <c r="BL41" s="5"/>
-      <c r="BM41" s="5"/>
-      <c r="BN41" s="5"/>
-      <c r="BO41" s="5"/>
-      <c r="BP41" s="5"/>
-      <c r="BQ41" s="5"/>
-      <c r="BR41" s="5"/>
-      <c r="BS41" s="5"/>
-      <c r="BT41" s="5"/>
-      <c r="BU41" s="5"/>
-      <c r="BV41" s="5"/>
-      <c r="BW41" s="5"/>
-      <c r="BX41" s="1"/>
-      <c r="BY41" s="1"/>
-      <c r="BZ41" s="1"/>
-      <c r="CA41" s="1"/>
-      <c r="CB41" s="1"/>
-      <c r="CC41" s="1"/>
-      <c r="CD41" s="1"/>
+      <c r="A41" s="6">
+        <v>1820</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="S41" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="T41" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="U41" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="W41" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X41" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="Y41" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="Z41" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="AA41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB41" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC41" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="AD41" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="AE41" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH41" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI41" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ41" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="AK41" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="AN41" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="AO41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP41" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AQ41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ41" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR41" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS41" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="BT41" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU41" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV41" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW41" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX41" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY41" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ41" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA41" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB41" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC41" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD41" s="6">
+        <v>3922</v>
+      </c>
     </row>
     <row r="42" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="5"/>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5"/>
-      <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
-      <c r="AB42" s="5"/>
-      <c r="AC42" s="5"/>
-      <c r="AD42" s="5"/>
-      <c r="AE42" s="5"/>
-      <c r="AF42" s="5"/>
-      <c r="AG42" s="5"/>
-      <c r="AH42" s="5"/>
-      <c r="AI42" s="5"/>
-      <c r="AJ42" s="5"/>
-      <c r="AK42" s="5"/>
-      <c r="AL42" s="5"/>
-      <c r="AM42" s="5"/>
-      <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
-      <c r="AP42" s="5"/>
-      <c r="AQ42" s="5"/>
-      <c r="AR42" s="5"/>
-      <c r="AS42" s="5"/>
-      <c r="AT42" s="5"/>
-      <c r="AU42" s="5"/>
-      <c r="AV42" s="5"/>
-      <c r="AW42" s="5"/>
-      <c r="AX42" s="5"/>
-      <c r="AY42" s="5"/>
-      <c r="AZ42" s="5"/>
-      <c r="BA42" s="5"/>
-      <c r="BB42" s="5"/>
-      <c r="BC42" s="5"/>
-      <c r="BD42" s="5"/>
-      <c r="BE42" s="5"/>
-      <c r="BF42" s="5"/>
-      <c r="BG42" s="5"/>
-      <c r="BH42" s="5"/>
-      <c r="BI42" s="5"/>
-      <c r="BJ42" s="5"/>
-      <c r="BK42" s="5"/>
-      <c r="BL42" s="5"/>
-      <c r="BM42" s="5"/>
-      <c r="BN42" s="5"/>
-      <c r="BO42" s="5"/>
-      <c r="BP42" s="5"/>
-      <c r="BQ42" s="5"/>
-      <c r="BR42" s="5"/>
-      <c r="BS42" s="5"/>
-      <c r="BT42" s="5"/>
-      <c r="BU42" s="5"/>
-      <c r="BV42" s="5"/>
-      <c r="BW42" s="5"/>
-      <c r="BX42" s="1"/>
-      <c r="BY42" s="1"/>
-      <c r="BZ42" s="1"/>
-      <c r="CA42" s="1"/>
-      <c r="CB42" s="1"/>
-      <c r="CC42" s="1"/>
-      <c r="CD42" s="1"/>
+      <c r="A42" s="6">
+        <v>1822</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="O42" s="6">
+        <v>0</v>
+      </c>
+      <c r="P42" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="S42" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="T42" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="U42" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="V42" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="W42" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="X42" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="Y42" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="Z42" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="AA42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB42" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC42" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="AD42" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="AE42" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH42" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="AI42" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="AK42" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="AN42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP42" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="AQ42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR42" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="AS42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS42" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="BT42" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="BU42" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV42" s="6">
+        <v>9890625370</v>
+      </c>
+      <c r="BW42" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX42" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY42" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ42" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA42" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB42" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC42" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD42" s="6" t="s">
+        <v>827</v>
+      </c>
     </row>
     <row r="43" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5"/>
-      <c r="AA43" s="5"/>
-      <c r="AB43" s="5"/>
-      <c r="AC43" s="5"/>
-      <c r="AD43" s="5"/>
-      <c r="AE43" s="5"/>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="5"/>
-      <c r="AH43" s="5"/>
-      <c r="AI43" s="5"/>
-      <c r="AJ43" s="5"/>
-      <c r="AK43" s="5"/>
-      <c r="AL43" s="5"/>
-      <c r="AM43" s="5"/>
-      <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
-      <c r="AP43" s="5"/>
-      <c r="AQ43" s="5"/>
-      <c r="AR43" s="5"/>
-      <c r="AS43" s="5"/>
-      <c r="AT43" s="5"/>
-      <c r="AU43" s="5"/>
-      <c r="AV43" s="5"/>
-      <c r="AW43" s="5"/>
-      <c r="AX43" s="5"/>
-      <c r="AY43" s="5"/>
-      <c r="AZ43" s="5"/>
-      <c r="BA43" s="5"/>
-      <c r="BB43" s="5"/>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="5"/>
-      <c r="BE43" s="5"/>
-      <c r="BF43" s="5"/>
-      <c r="BG43" s="5"/>
-      <c r="BH43" s="5"/>
-      <c r="BI43" s="5"/>
-      <c r="BJ43" s="5"/>
-      <c r="BK43" s="5"/>
-      <c r="BL43" s="5"/>
-      <c r="BM43" s="5"/>
-      <c r="BN43" s="5"/>
-      <c r="BO43" s="5"/>
-      <c r="BP43" s="5"/>
-      <c r="BQ43" s="5"/>
-      <c r="BR43" s="5"/>
-      <c r="BS43" s="5"/>
-      <c r="BT43" s="5"/>
-      <c r="BU43" s="5"/>
-      <c r="BV43" s="5"/>
-      <c r="BW43" s="5"/>
-      <c r="BX43" s="1"/>
-      <c r="BY43" s="1"/>
-      <c r="BZ43" s="1"/>
-      <c r="CA43" s="1"/>
-      <c r="CB43" s="1"/>
-      <c r="CC43" s="1"/>
-      <c r="CD43" s="1"/>
+      <c r="A43" s="6">
+        <v>1823</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O43" s="6">
+        <v>0</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="T43" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="U43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V43" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="W43" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X43" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="Y43" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="Z43" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="AA43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC43" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="AD43" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE43" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH43" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="AI43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>4</v>
+      </c>
+      <c r="AK43" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="AN43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP43" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AQ43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR43" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="AS43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY43" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="AZ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS43" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="BT43" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU43" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV43" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW43" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX43" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY43" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ43" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB43" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD43" s="6">
+        <v>5557</v>
+      </c>
     </row>
     <row r="44" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-      <c r="V44" s="5"/>
-      <c r="W44" s="5"/>
-      <c r="X44" s="5"/>
-      <c r="Y44" s="5"/>
-      <c r="Z44" s="5"/>
-      <c r="AA44" s="5"/>
-      <c r="AB44" s="5"/>
-      <c r="AC44" s="5"/>
-      <c r="AD44" s="5"/>
-      <c r="AE44" s="5"/>
-      <c r="AF44" s="5"/>
-      <c r="AG44" s="5"/>
-      <c r="AH44" s="5"/>
-      <c r="AI44" s="5"/>
-      <c r="AJ44" s="5"/>
-      <c r="AK44" s="5"/>
-      <c r="AL44" s="5"/>
-      <c r="AM44" s="5"/>
-      <c r="AN44" s="5"/>
-      <c r="AO44" s="5"/>
-      <c r="AP44" s="5"/>
-      <c r="AQ44" s="5"/>
-      <c r="AR44" s="5"/>
-      <c r="AS44" s="5"/>
-      <c r="AT44" s="5"/>
-      <c r="AU44" s="5"/>
-      <c r="AV44" s="5"/>
-      <c r="AW44" s="5"/>
-      <c r="AX44" s="5"/>
-      <c r="AY44" s="5"/>
-      <c r="AZ44" s="5"/>
-      <c r="BA44" s="5"/>
-      <c r="BB44" s="5"/>
-      <c r="BC44" s="5"/>
-      <c r="BD44" s="5"/>
-      <c r="BE44" s="5"/>
-      <c r="BF44" s="5"/>
-      <c r="BG44" s="5"/>
-      <c r="BH44" s="5"/>
-      <c r="BI44" s="5"/>
-      <c r="BJ44" s="5"/>
-      <c r="BK44" s="5"/>
-      <c r="BL44" s="5"/>
-      <c r="BM44" s="5"/>
-      <c r="BN44" s="5"/>
-      <c r="BO44" s="5"/>
-      <c r="BP44" s="5"/>
-      <c r="BQ44" s="5"/>
-      <c r="BR44" s="5"/>
-      <c r="BS44" s="5"/>
-      <c r="BT44" s="5"/>
-      <c r="BU44" s="5"/>
-      <c r="BV44" s="5"/>
-      <c r="BW44" s="5"/>
-      <c r="BX44" s="1"/>
-      <c r="BY44" s="1"/>
-      <c r="BZ44" s="1"/>
-      <c r="CA44" s="1"/>
-      <c r="CB44" s="1"/>
-      <c r="CC44" s="1"/>
-      <c r="CD44" s="1"/>
+      <c r="A44" s="6">
+        <v>1824</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="T44" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="U44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V44" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="W44" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X44" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="Y44" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="Z44" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC44" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="AD44" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="AE44" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="AF44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="AN44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="AO44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP44" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="AQ44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS44" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="BT44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU44" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV44" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW44" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX44" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY44" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ44" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB44" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD44" s="6">
+        <v>2415</v>
+      </c>
     </row>
     <row r="45" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-      <c r="U45" s="5"/>
-      <c r="V45" s="5"/>
-      <c r="W45" s="5"/>
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
-      <c r="AA45" s="5"/>
-      <c r="AB45" s="5"/>
-      <c r="AC45" s="5"/>
-      <c r="AD45" s="5"/>
-      <c r="AE45" s="5"/>
-      <c r="AF45" s="5"/>
-      <c r="AG45" s="5"/>
-      <c r="AH45" s="5"/>
-      <c r="AI45" s="5"/>
-      <c r="AJ45" s="5"/>
-      <c r="AK45" s="5"/>
-      <c r="AL45" s="5"/>
-      <c r="AM45" s="5"/>
-      <c r="AN45" s="5"/>
-      <c r="AO45" s="5"/>
-      <c r="AP45" s="5"/>
-      <c r="AQ45" s="5"/>
-      <c r="AR45" s="5"/>
-      <c r="AS45" s="5"/>
-      <c r="AT45" s="5"/>
-      <c r="AU45" s="5"/>
-      <c r="AV45" s="5"/>
-      <c r="AW45" s="5"/>
-      <c r="AX45" s="5"/>
-      <c r="AY45" s="5"/>
-      <c r="AZ45" s="5"/>
-      <c r="BA45" s="5"/>
-      <c r="BB45" s="5"/>
-      <c r="BC45" s="5"/>
-      <c r="BD45" s="5"/>
-      <c r="BE45" s="5"/>
-      <c r="BF45" s="5"/>
-      <c r="BG45" s="5"/>
-      <c r="BH45" s="5"/>
-      <c r="BI45" s="5"/>
-      <c r="BJ45" s="5"/>
-      <c r="BK45" s="5"/>
-      <c r="BL45" s="5"/>
-      <c r="BM45" s="5"/>
-      <c r="BN45" s="5"/>
-      <c r="BO45" s="5"/>
-      <c r="BP45" s="5"/>
-      <c r="BQ45" s="5"/>
-      <c r="BR45" s="5"/>
-      <c r="BS45" s="5"/>
-      <c r="BT45" s="5"/>
-      <c r="BU45" s="5"/>
-      <c r="BV45" s="5"/>
-      <c r="BW45" s="5"/>
-      <c r="BX45" s="1"/>
-      <c r="BY45" s="1"/>
-      <c r="BZ45" s="1"/>
-      <c r="CA45" s="1"/>
-      <c r="CB45" s="1"/>
-      <c r="CC45" s="1"/>
-      <c r="CD45" s="1"/>
+      <c r="A45" s="6">
+        <v>1828</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="S45" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="T45" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="U45" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="V45" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="W45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X45" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="Y45" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z45" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC45" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="AD45" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE45" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="AH45" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="AI45" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="AJ45" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="AN45" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="AO45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP45" s="6">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="AQ45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR45" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="AS45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS45" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="BT45" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU45" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV45" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW45" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX45" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY45" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ45" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB45" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD45" s="6">
+        <v>3279</v>
+      </c>
     </row>
     <row r="46" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5"/>
-      <c r="Z46" s="5"/>
-      <c r="AA46" s="5"/>
-      <c r="AB46" s="5"/>
-      <c r="AC46" s="5"/>
-      <c r="AD46" s="5"/>
-      <c r="AE46" s="5"/>
-      <c r="AF46" s="5"/>
-      <c r="AG46" s="5"/>
-      <c r="AH46" s="5"/>
-      <c r="AI46" s="5"/>
-      <c r="AJ46" s="5"/>
-      <c r="AK46" s="5"/>
-      <c r="AL46" s="5"/>
-      <c r="AM46" s="5"/>
-      <c r="AN46" s="5"/>
-      <c r="AO46" s="5"/>
-      <c r="AP46" s="5"/>
-      <c r="AQ46" s="5"/>
-      <c r="AR46" s="5"/>
-      <c r="AS46" s="5"/>
-      <c r="AT46" s="5"/>
-      <c r="AU46" s="5"/>
-      <c r="AV46" s="5"/>
-      <c r="AW46" s="5"/>
-      <c r="AX46" s="5"/>
-      <c r="AY46" s="5"/>
-      <c r="AZ46" s="5"/>
-      <c r="BA46" s="5"/>
-      <c r="BB46" s="5"/>
-      <c r="BC46" s="5"/>
-      <c r="BD46" s="5"/>
-      <c r="BE46" s="5"/>
-      <c r="BF46" s="5"/>
-      <c r="BG46" s="5"/>
-      <c r="BH46" s="5"/>
-      <c r="BI46" s="5"/>
-      <c r="BJ46" s="5"/>
-      <c r="BK46" s="5"/>
-      <c r="BL46" s="5"/>
-      <c r="BM46" s="5"/>
-      <c r="BN46" s="5"/>
-      <c r="BO46" s="5"/>
-      <c r="BP46" s="5"/>
-      <c r="BQ46" s="5"/>
-      <c r="BR46" s="5"/>
-      <c r="BS46" s="5"/>
-      <c r="BT46" s="5"/>
-      <c r="BU46" s="5"/>
-      <c r="BV46" s="5"/>
-      <c r="BW46" s="5"/>
-      <c r="BX46" s="1"/>
-      <c r="BY46" s="1"/>
-      <c r="BZ46" s="1"/>
-      <c r="CA46" s="1"/>
-      <c r="CB46" s="1"/>
-      <c r="CC46" s="1"/>
-      <c r="CD46" s="1"/>
+      <c r="A46" s="6">
+        <v>1829</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="O46" s="6">
+        <v>0</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>881</v>
+      </c>
+      <c r="T46" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="U46" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V46" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="W46" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X46" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="Y46" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="Z46" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="AA46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC46" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="AD46" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE46" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH46" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="AI46" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK46" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="AN46" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="AO46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP46" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="AQ46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR46" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="AS46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS46" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="BT46" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU46" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV46" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW46" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX46" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ46" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB46" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD46" s="6">
+        <v>4131</v>
+      </c>
     </row>
     <row r="47" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
-      <c r="U47" s="5"/>
-      <c r="V47" s="5"/>
-      <c r="W47" s="5"/>
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5"/>
-      <c r="AA47" s="5"/>
-      <c r="AB47" s="5"/>
-      <c r="AC47" s="5"/>
-      <c r="AD47" s="5"/>
-      <c r="AE47" s="5"/>
-      <c r="AF47" s="5"/>
-      <c r="AG47" s="5"/>
-      <c r="AH47" s="5"/>
-      <c r="AI47" s="5"/>
-      <c r="AJ47" s="5"/>
-      <c r="AK47" s="5"/>
-      <c r="AL47" s="5"/>
-      <c r="AM47" s="5"/>
-      <c r="AN47" s="5"/>
-      <c r="AO47" s="5"/>
-      <c r="AP47" s="5"/>
-      <c r="AQ47" s="5"/>
-      <c r="AR47" s="5"/>
-      <c r="AS47" s="5"/>
-      <c r="AT47" s="5"/>
-      <c r="AU47" s="5"/>
-      <c r="AV47" s="5"/>
-      <c r="AW47" s="5"/>
-      <c r="AX47" s="5"/>
-      <c r="AY47" s="5"/>
-      <c r="AZ47" s="5"/>
-      <c r="BA47" s="5"/>
-      <c r="BB47" s="5"/>
-      <c r="BC47" s="5"/>
-      <c r="BD47" s="5"/>
-      <c r="BE47" s="5"/>
-      <c r="BF47" s="5"/>
-      <c r="BG47" s="5"/>
-      <c r="BH47" s="5"/>
-      <c r="BI47" s="5"/>
-      <c r="BJ47" s="5"/>
-      <c r="BK47" s="5"/>
-      <c r="BL47" s="5"/>
-      <c r="BM47" s="5"/>
-      <c r="BN47" s="5"/>
-      <c r="BO47" s="5"/>
-      <c r="BP47" s="5"/>
-      <c r="BQ47" s="5"/>
-      <c r="BR47" s="5"/>
-      <c r="BS47" s="5"/>
-      <c r="BT47" s="5"/>
-      <c r="BU47" s="5"/>
-      <c r="BV47" s="5"/>
-      <c r="BW47" s="5"/>
-      <c r="BX47" s="1"/>
-      <c r="BY47" s="1"/>
-      <c r="BZ47" s="1"/>
-      <c r="CA47" s="1"/>
-      <c r="CB47" s="1"/>
-      <c r="CC47" s="1"/>
-      <c r="CD47" s="1"/>
+      <c r="A47" s="6">
+        <v>1830</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="O47" s="6">
+        <v>0</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="S47" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="T47" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="U47" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="V47" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="W47" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X47" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="Y47" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="Z47" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="AA47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC47" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="AD47" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE47" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="AF47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="AH47" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="AI47" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ47" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="AK47" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="AN47" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="AO47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP47" s="6">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AQ47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR47" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="AS47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS47" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="BT47" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU47" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV47" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW47" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX47" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ47" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB47" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD47" s="6">
+        <v>852</v>
+      </c>
     </row>
     <row r="48" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-      <c r="U48" s="5"/>
-      <c r="V48" s="5"/>
-      <c r="W48" s="5"/>
-      <c r="X48" s="5"/>
-      <c r="Y48" s="5"/>
-      <c r="Z48" s="5"/>
-      <c r="AA48" s="5"/>
-      <c r="AB48" s="5"/>
-      <c r="AC48" s="5"/>
-      <c r="AD48" s="5"/>
-      <c r="AE48" s="5"/>
-      <c r="AF48" s="5"/>
-      <c r="AG48" s="5"/>
-      <c r="AH48" s="5"/>
-      <c r="AI48" s="5"/>
-      <c r="AJ48" s="5"/>
-      <c r="AK48" s="5"/>
-      <c r="AL48" s="5"/>
-      <c r="AM48" s="5"/>
-      <c r="AN48" s="5"/>
-      <c r="AO48" s="5"/>
-      <c r="AP48" s="5"/>
-      <c r="AQ48" s="5"/>
-      <c r="AR48" s="5"/>
-      <c r="AS48" s="5"/>
-      <c r="AT48" s="5"/>
-      <c r="AU48" s="5"/>
-      <c r="AV48" s="5"/>
-      <c r="AW48" s="5"/>
-      <c r="AX48" s="5"/>
-      <c r="AY48" s="5"/>
-      <c r="AZ48" s="5"/>
-      <c r="BA48" s="5"/>
-      <c r="BB48" s="5"/>
-      <c r="BC48" s="5"/>
-      <c r="BD48" s="5"/>
-      <c r="BE48" s="5"/>
-      <c r="BF48" s="5"/>
-      <c r="BG48" s="5"/>
-      <c r="BH48" s="5"/>
-      <c r="BI48" s="5"/>
-      <c r="BJ48" s="5"/>
-      <c r="BK48" s="5"/>
-      <c r="BL48" s="5"/>
-      <c r="BM48" s="5"/>
-      <c r="BN48" s="5"/>
-      <c r="BO48" s="5"/>
-      <c r="BP48" s="5"/>
-      <c r="BQ48" s="5"/>
-      <c r="BR48" s="5"/>
-      <c r="BS48" s="5"/>
-      <c r="BT48" s="5"/>
-      <c r="BU48" s="5"/>
-      <c r="BV48" s="5"/>
-      <c r="BW48" s="5"/>
-      <c r="BX48" s="1"/>
-      <c r="BY48" s="1"/>
-      <c r="BZ48" s="1"/>
-      <c r="CA48" s="1"/>
-      <c r="CB48" s="1"/>
-      <c r="CC48" s="1"/>
-      <c r="CD48" s="1"/>
+      <c r="A48" s="6">
+        <v>1831</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="S48" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="T48" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="U48" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="V48" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="W48" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="X48" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="Y48" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="Z48" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="AA48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC48" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="AD48" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="AE48" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="AF48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="AH48" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="AI48" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="AJ48" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK48" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="AN48" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="AO48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP48" s="6">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="AQ48" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR48" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="AS48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY48" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS48" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="BT48" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="BU48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV48" s="6">
+        <v>9822220725</v>
+      </c>
+      <c r="BW48" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX48" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY48" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ48" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA48" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB48" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC48" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD48" s="6">
+        <v>3429</v>
+      </c>
     </row>
     <row r="49" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
-      <c r="U49" s="5"/>
-      <c r="V49" s="5"/>
-      <c r="W49" s="5"/>
-      <c r="X49" s="5"/>
-      <c r="Y49" s="5"/>
-      <c r="Z49" s="5"/>
-      <c r="AA49" s="5"/>
-      <c r="AB49" s="5"/>
-      <c r="AC49" s="5"/>
-      <c r="AD49" s="5"/>
-      <c r="AE49" s="5"/>
-      <c r="AF49" s="5"/>
-      <c r="AG49" s="5"/>
-      <c r="AH49" s="5"/>
-      <c r="AI49" s="5"/>
-      <c r="AJ49" s="5"/>
-      <c r="AK49" s="5"/>
-      <c r="AL49" s="5"/>
-      <c r="AM49" s="5"/>
-      <c r="AN49" s="5"/>
-      <c r="AO49" s="5"/>
-      <c r="AP49" s="5"/>
-      <c r="AQ49" s="5"/>
-      <c r="AR49" s="5"/>
-      <c r="AS49" s="5"/>
-      <c r="AT49" s="5"/>
-      <c r="AU49" s="5"/>
-      <c r="AV49" s="5"/>
-      <c r="AW49" s="5"/>
-      <c r="AX49" s="5"/>
-      <c r="AY49" s="5"/>
-      <c r="AZ49" s="5"/>
-      <c r="BA49" s="5"/>
-      <c r="BB49" s="5"/>
-      <c r="BC49" s="5"/>
-      <c r="BD49" s="5"/>
-      <c r="BE49" s="5"/>
-      <c r="BF49" s="5"/>
-      <c r="BG49" s="5"/>
-      <c r="BH49" s="5"/>
-      <c r="BI49" s="5"/>
-      <c r="BJ49" s="5"/>
-      <c r="BK49" s="5"/>
-      <c r="BL49" s="5"/>
-      <c r="BM49" s="5"/>
-      <c r="BN49" s="5"/>
-      <c r="BO49" s="5"/>
-      <c r="BP49" s="5"/>
-      <c r="BQ49" s="5"/>
-      <c r="BR49" s="5"/>
-      <c r="BS49" s="5"/>
-      <c r="BT49" s="5"/>
-      <c r="BU49" s="5"/>
-      <c r="BV49" s="5"/>
-      <c r="BW49" s="5"/>
-      <c r="BX49" s="1"/>
-      <c r="BY49" s="1"/>
-      <c r="BZ49" s="1"/>
-      <c r="CA49" s="1"/>
-      <c r="CB49" s="1"/>
-      <c r="CC49" s="1"/>
-      <c r="CD49" s="1"/>
+      <c r="A49" s="6">
+        <v>1856</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="O49" s="6">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="T49" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="U49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V49" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="W49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X49" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="Y49" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="Z49" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="AA49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB49" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC49" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="AD49" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="AE49" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="AF49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH49" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="AI49" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="AJ49" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK49" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="AN49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP49" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="AQ49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY49" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ49" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR49" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT49" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV49" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW49" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX49" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ49" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB49" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD49" s="6">
+        <v>3702</v>
+      </c>
     </row>
     <row r="50" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
-      <c r="U50" s="5"/>
-      <c r="V50" s="5"/>
-      <c r="W50" s="5"/>
-      <c r="X50" s="5"/>
-      <c r="Y50" s="5"/>
-      <c r="Z50" s="5"/>
-      <c r="AA50" s="5"/>
-      <c r="AB50" s="5"/>
-      <c r="AC50" s="5"/>
-      <c r="AD50" s="5"/>
-      <c r="AE50" s="5"/>
-      <c r="AF50" s="5"/>
-      <c r="AG50" s="5"/>
-      <c r="AH50" s="5"/>
-      <c r="AI50" s="5"/>
-      <c r="AJ50" s="5"/>
-      <c r="AK50" s="5"/>
-      <c r="AL50" s="5"/>
-      <c r="AM50" s="5"/>
-      <c r="AN50" s="5"/>
-      <c r="AO50" s="5"/>
-      <c r="AP50" s="5"/>
-      <c r="AQ50" s="5"/>
-      <c r="AR50" s="5"/>
-      <c r="AS50" s="5"/>
-      <c r="AT50" s="5"/>
-      <c r="AU50" s="5"/>
-      <c r="AV50" s="5"/>
-      <c r="AW50" s="5"/>
-      <c r="AX50" s="5"/>
-      <c r="AY50" s="5"/>
-      <c r="AZ50" s="5"/>
-      <c r="BA50" s="5"/>
-      <c r="BB50" s="5"/>
-      <c r="BC50" s="5"/>
-      <c r="BD50" s="5"/>
-      <c r="BE50" s="5"/>
-      <c r="BF50" s="5"/>
-      <c r="BG50" s="5"/>
-      <c r="BH50" s="5"/>
-      <c r="BI50" s="5"/>
-      <c r="BJ50" s="5"/>
-      <c r="BK50" s="5"/>
-      <c r="BL50" s="5"/>
-      <c r="BM50" s="5"/>
-      <c r="BN50" s="5"/>
-      <c r="BO50" s="5"/>
-      <c r="BP50" s="5"/>
-      <c r="BQ50" s="5"/>
-      <c r="BR50" s="5"/>
-      <c r="BS50" s="5"/>
-      <c r="BT50" s="5"/>
-      <c r="BU50" s="5"/>
-      <c r="BV50" s="5"/>
-      <c r="BW50" s="5"/>
-      <c r="BX50" s="1"/>
-      <c r="BY50" s="1"/>
-      <c r="BZ50" s="1"/>
-      <c r="CA50" s="1"/>
-      <c r="CB50" s="1"/>
-      <c r="CC50" s="1"/>
-      <c r="CD50" s="1"/>
+      <c r="A50" s="6">
+        <v>1857</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="O50" s="6">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="S50" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="T50" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="U50" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V50" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="W50" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X50" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="Y50" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="Z50" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="AA50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC50" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="AD50" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="AE50" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH50" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="AI50" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="AN50" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP50" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="AQ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY50" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS50" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="BT50" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU50" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV50" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW50" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX50" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ50" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA50" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB50" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC50" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD50" s="6">
+        <v>2745</v>
+      </c>
     </row>
     <row r="51" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-      <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
-      <c r="U51" s="5"/>
-      <c r="V51" s="5"/>
-      <c r="W51" s="5"/>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5"/>
-      <c r="Z51" s="5"/>
-      <c r="AA51" s="5"/>
-      <c r="AB51" s="5"/>
-      <c r="AC51" s="5"/>
-      <c r="AD51" s="5"/>
-      <c r="AE51" s="5"/>
-      <c r="AF51" s="5"/>
-      <c r="AG51" s="5"/>
-      <c r="AH51" s="5"/>
-      <c r="AI51" s="5"/>
-      <c r="AJ51" s="5"/>
-      <c r="AK51" s="5"/>
-      <c r="AL51" s="5"/>
-      <c r="AM51" s="5"/>
-      <c r="AN51" s="5"/>
-      <c r="AO51" s="5"/>
-      <c r="AP51" s="5"/>
-      <c r="AQ51" s="5"/>
-      <c r="AR51" s="5"/>
-      <c r="AS51" s="5"/>
-      <c r="AT51" s="5"/>
-      <c r="AU51" s="5"/>
-      <c r="AV51" s="5"/>
-      <c r="AW51" s="5"/>
-      <c r="AX51" s="5"/>
-      <c r="AY51" s="5"/>
-      <c r="AZ51" s="5"/>
-      <c r="BA51" s="5"/>
-      <c r="BB51" s="5"/>
-      <c r="BC51" s="5"/>
-      <c r="BD51" s="5"/>
-      <c r="BE51" s="5"/>
-      <c r="BF51" s="5"/>
-      <c r="BG51" s="5"/>
-      <c r="BH51" s="5"/>
-      <c r="BI51" s="5"/>
-      <c r="BJ51" s="5"/>
-      <c r="BK51" s="5"/>
-      <c r="BL51" s="5"/>
-      <c r="BM51" s="5"/>
-      <c r="BN51" s="5"/>
-      <c r="BO51" s="5"/>
-      <c r="BP51" s="5"/>
-      <c r="BQ51" s="5"/>
-      <c r="BR51" s="5"/>
-      <c r="BS51" s="5"/>
-      <c r="BT51" s="5"/>
-      <c r="BU51" s="5"/>
-      <c r="BV51" s="5"/>
-      <c r="BW51" s="5"/>
-      <c r="BX51" s="1"/>
-      <c r="BY51" s="1"/>
-      <c r="BZ51" s="1"/>
-      <c r="CA51" s="1"/>
-      <c r="CB51" s="1"/>
-      <c r="CC51" s="1"/>
-      <c r="CD51" s="1"/>
+      <c r="A51" s="6">
+        <v>1858</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="S51" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="T51" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="U51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V51" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="W51" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X51" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="Y51" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="Z51" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="AA51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB51" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC51" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="AD51" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="AE51" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH51" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="AI51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK51" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="AN51" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP51" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="AQ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ51" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR51" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS51" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="BT51" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV51" s="6">
+        <v>9423144198</v>
+      </c>
+      <c r="BW51" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="BX51" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY51" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ51" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA51" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB51" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="CC51" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD51" s="6">
+        <v>3214</v>
+      </c>
     </row>
     <row r="52" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5"/>
-      <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
-      <c r="U52" s="5"/>
-      <c r="V52" s="5"/>
-      <c r="W52" s="5"/>
-      <c r="X52" s="5"/>
-      <c r="Y52" s="5"/>
-      <c r="Z52" s="5"/>
-      <c r="AA52" s="5"/>
-      <c r="AB52" s="5"/>
-      <c r="AC52" s="5"/>
-      <c r="AD52" s="5"/>
-      <c r="AE52" s="5"/>
-      <c r="AF52" s="5"/>
-      <c r="AG52" s="5"/>
-      <c r="AH52" s="5"/>
-      <c r="AI52" s="5"/>
-      <c r="AJ52" s="5"/>
-      <c r="AK52" s="5"/>
-      <c r="AL52" s="5"/>
-      <c r="AM52" s="5"/>
-      <c r="AN52" s="5"/>
-      <c r="AO52" s="5"/>
-      <c r="AP52" s="5"/>
-      <c r="AQ52" s="5"/>
-      <c r="AR52" s="5"/>
-      <c r="AS52" s="5"/>
-      <c r="AT52" s="5"/>
-      <c r="AU52" s="5"/>
-      <c r="AV52" s="5"/>
-      <c r="AW52" s="5"/>
-      <c r="AX52" s="5"/>
-      <c r="AY52" s="5"/>
-      <c r="AZ52" s="5"/>
-      <c r="BA52" s="5"/>
-      <c r="BB52" s="5"/>
-      <c r="BC52" s="5"/>
-      <c r="BD52" s="5"/>
-      <c r="BE52" s="5"/>
-      <c r="BF52" s="5"/>
-      <c r="BG52" s="5"/>
-      <c r="BH52" s="5"/>
-      <c r="BI52" s="5"/>
-      <c r="BJ52" s="5"/>
-      <c r="BK52" s="5"/>
-      <c r="BL52" s="5"/>
-      <c r="BM52" s="5"/>
-      <c r="BN52" s="5"/>
-      <c r="BO52" s="5"/>
-      <c r="BP52" s="5"/>
-      <c r="BQ52" s="5"/>
-      <c r="BR52" s="5"/>
-      <c r="BS52" s="5"/>
-      <c r="BT52" s="5"/>
-      <c r="BU52" s="5"/>
-      <c r="BV52" s="5"/>
-      <c r="BW52" s="5"/>
-      <c r="BX52" s="1"/>
-      <c r="BY52" s="1"/>
-      <c r="BZ52" s="1"/>
-      <c r="CA52" s="1"/>
-      <c r="CB52" s="1"/>
-      <c r="CC52" s="1"/>
-      <c r="CD52" s="1"/>
+      <c r="A52" s="6">
+        <v>2307</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="S52" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="T52" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="U52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V52" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="W52" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="X52" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="Y52" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="Z52" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="AA52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB52" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC52" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="AD52" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE52" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH52" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="AI52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="AK52" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="AN52" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="AO52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP52" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="AQ52" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR52" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="AS52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT52" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="BU52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV52" s="6">
+        <v>9822220725</v>
+      </c>
+      <c r="BW52" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="BX52" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY52" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BZ52" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="CA52" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CB52" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="CC52" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD52" s="6">
+        <v>2090</v>
+      </c>
     </row>
     <row r="53" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
@@ -15465,90 +18477,6 @@
       <c r="CC75" s="1"/>
       <c r="CD75" s="1"/>
     </row>
-    <row r="76" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="5"/>
-      <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
-      <c r="U76" s="5"/>
-      <c r="V76" s="5"/>
-      <c r="W76" s="5"/>
-      <c r="X76" s="5"/>
-      <c r="Y76" s="5"/>
-      <c r="Z76" s="5"/>
-      <c r="AA76" s="5"/>
-      <c r="AB76" s="5"/>
-      <c r="AC76" s="5"/>
-      <c r="AD76" s="5"/>
-      <c r="AE76" s="5"/>
-      <c r="AF76" s="5"/>
-      <c r="AG76" s="5"/>
-      <c r="AH76" s="5"/>
-      <c r="AI76" s="5"/>
-      <c r="AJ76" s="5"/>
-      <c r="AK76" s="5"/>
-      <c r="AL76" s="5"/>
-      <c r="AM76" s="5"/>
-      <c r="AN76" s="5"/>
-      <c r="AO76" s="5"/>
-      <c r="AP76" s="5"/>
-      <c r="AQ76" s="5"/>
-      <c r="AR76" s="5"/>
-      <c r="AS76" s="5"/>
-      <c r="AT76" s="5"/>
-      <c r="AU76" s="5"/>
-      <c r="AV76" s="5"/>
-      <c r="AW76" s="5"/>
-      <c r="AX76" s="5"/>
-      <c r="AY76" s="5"/>
-      <c r="AZ76" s="5"/>
-      <c r="BA76" s="5"/>
-      <c r="BB76" s="5"/>
-      <c r="BC76" s="5"/>
-      <c r="BD76" s="5"/>
-      <c r="BE76" s="5"/>
-      <c r="BF76" s="5"/>
-      <c r="BG76" s="5"/>
-      <c r="BH76" s="5"/>
-      <c r="BI76" s="5"/>
-      <c r="BJ76" s="5"/>
-      <c r="BK76" s="5"/>
-      <c r="BL76" s="5"/>
-      <c r="BM76" s="5"/>
-      <c r="BN76" s="5"/>
-      <c r="BO76" s="5"/>
-      <c r="BP76" s="5"/>
-      <c r="BQ76" s="5"/>
-      <c r="BR76" s="5"/>
-      <c r="BS76" s="5"/>
-      <c r="BT76" s="5"/>
-      <c r="BU76" s="5"/>
-      <c r="BV76" s="5"/>
-      <c r="BW76" s="5"/>
-      <c r="BX76" s="1"/>
-      <c r="BY76" s="1"/>
-      <c r="BZ76" s="1"/>
-      <c r="CA76" s="1"/>
-      <c r="CB76" s="1"/>
-      <c r="CC76" s="1"/>
-      <c r="CD76" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
